--- a/tests/fixtures/ratio_z1_2026-04-11.xlsx
+++ b/tests/fixtures/ratio_z1_2026-04-11.xlsx
@@ -8,9 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="invalid_data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="valid_data" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="calc_data" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="merged_data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -979,20 +977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,32 +998,27 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>concept_ratio</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>concept_num</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>concept_den</t>
-        </is>
-      </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>value_num</t>
+          <t>concept_pos</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>value_den</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>value_ratio</t>
+          <t>concept_name</t>
         </is>
       </c>
     </row>
@@ -1060,27 +1040,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ebitda2Sales</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>175</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SalesNet</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>150</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.15</v>
+          <t>MaterialCosts2DirectLabor</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1101,27 +1080,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ebitda2TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>175</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>150</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1150</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.1304347826086956</v>
+          <t>Sales2DirectLabor</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -1142,27 +1120,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MaterialCosts2DirectLabor</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MaterialCosts</t>
-        </is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>150</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DirectLabor</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>300</v>
-      </c>
-      <c r="H4" t="n">
-        <v>175</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.714285714285714</v>
+          <t>Ebitda2Sales</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1183,27 +1160,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sales2DirectLabor</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SalesNet</t>
-        </is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>150</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DirectLabor</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>175</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5.714285714285714</v>
+          <t>Ebitda2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1224,27 +1200,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Sales2MaterialCosts</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>SalesNet</t>
-        </is>
+          <t>MaterialCosts</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>MaterialCosts2DirectLabor</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>MaterialCosts</t>
         </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H6" t="n">
-        <v>300</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.333333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -1265,27 +1240,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sales2TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SalesNet</t>
-        </is>
+          <t>MaterialCosts</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1150</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.8695652173913043</v>
+          <t>Sales2MaterialCosts</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>MaterialCosts</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1296,7 +1270,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>q2020-2</t>
+          <t>q2020-1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1306,27 +1280,26 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ebitda2Sales</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1000</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SalesNet</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>120</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.1090909090909091</v>
+          <t>Sales2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1337,7 +1310,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>q2020-2</t>
+          <t>q2020-1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1347,27 +1320,26 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ebitda2TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>120</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.12</v>
+          <t>Sales2DirectLabor</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1378,7 +1350,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>q2020-2</t>
+          <t>q2020-1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1388,27 +1360,26 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sales2TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>SalesNet</t>
-        </is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1000</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.1</v>
+          <t>Sales2MaterialCosts</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1419,37 +1390,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>q2020-2</t>
+          <t>q2020-1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>qrtr</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MaterialCosts2DirectLabor</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MaterialCosts</t>
-        </is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1000</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DirectLabor</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>50</v>
-      </c>
-      <c r="H11" t="n">
-        <v>40</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.25</v>
+          <t>Ebitda2Sales</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1460,37 +1430,36 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>q2020-2</t>
+          <t>q2020-1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>qrtr</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sales2DirectLabor</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>SalesNet</t>
-        </is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1150</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DirectLabor</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>275</v>
-      </c>
-      <c r="H12" t="n">
-        <v>40</v>
-      </c>
-      <c r="I12" t="n">
-        <v>6.875</v>
+          <t>Sales2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1501,48 +1470,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>q2020-2</t>
+          <t>q2020-1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>qrtr</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sales2MaterialCosts</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>SalesNet</t>
-        </is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1150</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MaterialCosts</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>275</v>
-      </c>
-      <c r="H13" t="n">
-        <v>50</v>
-      </c>
-      <c r="I13" t="n">
-        <v>5.5</v>
+          <t>Ebitda2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cieB</t>
+          <t>cieA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>q2020-1</t>
+          <t>q2020-2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1552,38 +1520,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ebitda2TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
           <t>EBITDA</t>
         </is>
       </c>
+      <c r="E14" t="n">
+        <v>120</v>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>150</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1150</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.1304347826086956</v>
+          <t>Ebitda2Sales</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cieB</t>
+          <t>cieA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>q2020-1</t>
+          <t>q2020-2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1593,33 +1560,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sales2TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>SalesNet</t>
-        </is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>120</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1150</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
+          <t>Ebitda2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>cieC</t>
+          <t>cieA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1634,33 +1600,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ebitda2Sales</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1100</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SalesNet</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>1e-07</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1e-07</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
+          <t>Sales2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>cieC</t>
+          <t>cieA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1675,33 +1640,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ebitda2TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1100</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>1e-07</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I17" t="n">
-        <v>9.999999999999999e-11</v>
+          <t>Sales2DirectLabor</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cieC</t>
+          <t>cieA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1716,867 +1680,1422 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sales2TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>SalesNet</t>
-        </is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1100</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>1e-07</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I18" t="n">
-        <v>9.999999999999999e-11</v>
+          <t>Sales2MaterialCosts</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1100</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ebitda2Sales</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Sales2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ebitda2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>qrtr</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>40</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>MaterialCosts2DirectLabor</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>qrtr</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>40</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Sales2DirectLabor</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>qrtr</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>MaterialCosts</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>MaterialCosts2DirectLabor</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>MaterialCosts</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>qrtr</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MaterialCosts</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>50</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Sales2MaterialCosts</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>MaterialCosts</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>qrtr</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>275</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Sales2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>qrtr</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>275</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sales2DirectLabor</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>qrtr</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>275</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Sales2MaterialCosts</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>qrtr</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>275</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ebitda2Sales</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>MaterialCosts2DirectLabor</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Sales2DirectLabor</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>150</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ebitda2Sales</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>150</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ebitda2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>MaterialCosts</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>MaterialCosts2DirectLabor</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>MaterialCosts</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>MaterialCosts</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Sales2MaterialCosts</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>MaterialCosts</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Sales2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Sales2DirectLabor</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Sales2MaterialCosts</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ebitda2Sales</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1150</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Sales2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1150</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ebitda2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>cieC</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>q2020-2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ebitda2Sales</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ebitda2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Sales2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Sales2DirectLabor</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Sales2MaterialCosts</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ebitda2Sales</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>SalesNet</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Sales2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Ebitda2TangibleAssetsNoncash</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>TangibleAssetsNoncash</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
         <is>
           <t>qrtr</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>160</v>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>MaterialCosts2DirectLabor</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>qrtr</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>160</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Sales2DirectLabor</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>concept_den</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>DirectLabor</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>qrtr</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>MaterialCosts</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>DirectLabor</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
+      <c r="E52" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="n">
-        <v>160</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>MaterialCosts2DirectLabor</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>concept_num</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>MaterialCosts</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>qrtr</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>MaterialCosts</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
         <v>0</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>entity</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>pertype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>period</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>concept_ratio</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>concept_num</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Sales2MaterialCosts</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
         <is>
           <t>concept_den</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>value_num</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>value_den</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>value_ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>cieA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>q2020-1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Ebitda2Sales</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>SalesNet</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>150</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>cieA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>q2020-1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Ebitda2TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>150</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1150</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.1304347826086956</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cieA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>q2020-1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>MaterialCosts2DirectLabor</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>MaterialCosts</t>
         </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>DirectLabor</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>300</v>
-      </c>
-      <c r="H4" t="n">
-        <v>175</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.714285714285714</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cieA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>q2020-1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Sales2DirectLabor</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>SalesNet</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>DirectLabor</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>175</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5.714285714285714</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cieA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>q2020-1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Sales2MaterialCosts</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>SalesNet</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>MaterialCosts</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H6" t="n">
-        <v>300</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3.333333333333333</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cieA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>q2020-1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Sales2TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SalesNet</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1150</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.8695652173913043</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cieA</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>q2020-2</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Ebitda2Sales</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SalesNet</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>120</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1100</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.1090909090909091</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cieA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>q2020-2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Ebitda2TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>120</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cieA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>q2020-2</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Sales2TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>SalesNet</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1100</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>cieA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>q2020-2</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>qrtr</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>MaterialCosts2DirectLabor</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MaterialCosts</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>DirectLabor</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>50</v>
-      </c>
-      <c r="H11" t="n">
-        <v>40</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>cieA</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>q2020-2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>qrtr</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Sales2DirectLabor</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>SalesNet</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>DirectLabor</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>275</v>
-      </c>
-      <c r="H12" t="n">
-        <v>40</v>
-      </c>
-      <c r="I12" t="n">
-        <v>6.875</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>cieA</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>q2020-2</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>qrtr</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Sales2MaterialCosts</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>SalesNet</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>MaterialCosts</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>275</v>
-      </c>
-      <c r="H13" t="n">
-        <v>50</v>
-      </c>
-      <c r="I13" t="n">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>cieB</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>q2020-1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Ebitda2TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>150</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1150</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.1304347826086956</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cieB</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>q2020-1</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Sales2TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>SalesNet</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1150</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cieC</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>q2020-2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Ebitda2Sales</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SalesNet</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>1e-07</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1e-07</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cieC</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>q2020-2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Ebitda2TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>1e-07</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I17" t="n">
-        <v>9.999999999999999e-11</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cieC</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>q2020-2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Sales2TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>SalesNet</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>TangibleAssetsNoncash</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>1e-07</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I18" t="n">
-        <v>9.999999999999999e-11</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cieC</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>q2020-2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>qrtr</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>MaterialCosts2DirectLabor</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>MaterialCosts</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>DirectLabor</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>160</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
